--- a/模版/非身份证信息需求.xlsx
+++ b/模版/非身份证信息需求.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="3"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="填写要求"/>
@@ -178,7 +178,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -217,6 +217,12 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="12"/>
       <color rgb="FFff0000"/>
       <name val="等线 (正文)"/>
@@ -250,7 +256,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -288,16 +294,19 @@
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
@@ -618,111 +627,111 @@
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="23.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>16</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="23.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>17</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="23.25">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="16" t="s">
         <v>18</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="20.25">
-      <c r="A4" s="16"/>
+      <c r="A4" s="17"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="23.25">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="16" t="s">
         <v>19</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="20.25">
-      <c r="A6" s="16"/>
+      <c r="A6" s="17"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="23.25">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="18" t="s">
         <v>20</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="20.25">
-      <c r="A8" s="16"/>
+      <c r="A8" s="17"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="23.25">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="18" t="s">
         <v>21</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="20.25">
-      <c r="A10" s="16"/>
+      <c r="A10" s="17"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="23.25">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="18" t="s">
         <v>22</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="23.25">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="16" t="s">
         <v>23</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="23.25">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="16" t="s">
         <v>24</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="23.25">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="16" t="s">
         <v>25</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="23.25">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="18" t="s">
         <v>26</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="23.25">
-      <c r="A16" s="18"/>
+      <c r="A16" s="19"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="23.25">
-      <c r="A17" s="17" t="s">
+      <c r="A17" s="18" t="s">
         <v>27</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="23.25">
-      <c r="A18" s="18"/>
+      <c r="A18" s="19"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="23.25">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="18" t="s">
         <v>28</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="23.25">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="18" t="s">
         <v>29</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="23.25">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="18" t="s">
         <v>30</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="23.25">
-      <c r="A22" s="18"/>
+      <c r="A22" s="19"/>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="23.25">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="18" t="s">
         <v>31</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="17.25">
-      <c r="A24" s="19"/>
+      <c r="A24" s="20"/>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="23.25">
-      <c r="A25" s="17" t="s">
+      <c r="A25" s="18" t="s">
         <v>32</v>
       </c>
     </row>
@@ -730,7 +739,7 @@
       <c r="A26" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="23.25">
-      <c r="A27" s="17" t="s">
+      <c r="A27" s="18" t="s">
         <v>33</v>
       </c>
     </row>
@@ -738,7 +747,7 @@
       <c r="A28" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="23.25">
-      <c r="A29" s="17" t="s">
+      <c r="A29" s="18" t="s">
         <v>34</v>
       </c>
     </row>
@@ -746,12 +755,12 @@
       <c r="A30" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="17.25">
-      <c r="A31" s="17" t="s">
+      <c r="A31" s="18" t="s">
         <v>35</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="17.25">
-      <c r="A32" s="17" t="s">
+      <c r="A32" s="18" t="s">
         <v>36</v>
       </c>
     </row>
@@ -759,12 +768,12 @@
       <c r="A33" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="17.25">
-      <c r="A34" s="17" t="s">
+      <c r="A34" s="18" t="s">
         <v>37</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="17.25">
-      <c r="A35" s="17" t="s">
+      <c r="A35" s="18" t="s">
         <v>38</v>
       </c>
     </row>
@@ -772,7 +781,7 @@
       <c r="A36" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="17.25">
-      <c r="A37" s="17" t="s">
+      <c r="A37" s="18" t="s">
         <v>39</v>
       </c>
     </row>
@@ -780,7 +789,7 @@
       <c r="A38" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="17.25">
-      <c r="A39" s="17" t="s">
+      <c r="A39" s="18" t="s">
         <v>40</v>
       </c>
     </row>
@@ -788,17 +797,17 @@
       <c r="A40" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="17.25">
-      <c r="A41" s="17" t="s">
+      <c r="A41" s="18" t="s">
         <v>41</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="17.25">
-      <c r="A42" s="17" t="s">
+      <c r="A42" s="18" t="s">
         <v>42</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="17.25">
-      <c r="A43" s="17" t="s">
+      <c r="A43" s="18" t="s">
         <v>43</v>
       </c>
     </row>
@@ -806,12 +815,12 @@
       <c r="A44" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="17.25">
-      <c r="A45" s="17" t="s">
+      <c r="A45" s="18" t="s">
         <v>44</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="17.25">
-      <c r="A46" s="17" t="s">
+      <c r="A46" s="18" t="s">
         <v>45</v>
       </c>
     </row>
@@ -819,7 +828,7 @@
       <c r="A47" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="17.25">
-      <c r="A48" s="17" t="s">
+      <c r="A48" s="18" t="s">
         <v>46</v>
       </c>
     </row>
@@ -827,7 +836,7 @@
       <c r="A49" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="17.25">
-      <c r="A50" s="17" t="s">
+      <c r="A50" s="18" t="s">
         <v>47</v>
       </c>
     </row>
@@ -835,12 +844,12 @@
       <c r="A51" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="17.25">
-      <c r="A52" s="17" t="s">
+      <c r="A52" s="18" t="s">
         <v>48</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="17.25">
-      <c r="A53" s="17" t="s">
+      <c r="A53" s="18" t="s">
         <v>49</v>
       </c>
     </row>
@@ -861,7 +870,7 @@
     <col min="2" max="2" style="11" width="19.719285714285714" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="11" width="21.862142857142857" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="11" width="48.71928571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="14" width="75.14785714285713" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="15" width="75.14785714285713" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="4" width="9.147857142857141" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="8" max="8" style="4" width="12.43357142857143" customWidth="1" bestFit="1"/>
@@ -885,7 +894,7 @@
       <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="13"/>
+      <c r="E1" s="14"/>
       <c r="F1" s="7"/>
       <c r="G1" s="7"/>
       <c r="H1" s="7"/>
@@ -1100,7 +1109,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="11" width="10.862142857142858" customWidth="1" bestFit="1"/>
@@ -1116,7 +1125,7 @@
     <col min="11" max="11" style="12" width="43.86214285714286" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="23.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1151,7 +1160,7 @@
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="23.25">
       <c r="A2" s="5"/>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -1164,7 +1173,7 @@
       <c r="J2" s="9"/>
       <c r="K2" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="23.25">
       <c r="A3" s="5"/>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -1177,7 +1186,7 @@
       <c r="J3" s="9"/>
       <c r="K3" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="23.25">
       <c r="A4" s="5"/>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -1190,7 +1199,7 @@
       <c r="J4" s="9"/>
       <c r="K4" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="23.25">
       <c r="A5" s="5"/>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -1203,7 +1212,7 @@
       <c r="J5" s="9"/>
       <c r="K5" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="23.25">
       <c r="A6" s="5"/>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -1216,7 +1225,7 @@
       <c r="J6" s="9"/>
       <c r="K6" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="23.25">
       <c r="A7" s="5"/>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
@@ -1229,7 +1238,7 @@
       <c r="J7" s="9"/>
       <c r="K7" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="23.25">
       <c r="A8" s="5"/>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
@@ -1242,7 +1251,7 @@
       <c r="J8" s="9"/>
       <c r="K8" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="23.25">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -1255,7 +1264,7 @@
       <c r="J9" s="9"/>
       <c r="K9" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="23.25">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -1268,7 +1277,7 @@
       <c r="J10" s="9"/>
       <c r="K10" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="23.25">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -1281,7 +1290,7 @@
       <c r="J11" s="9"/>
       <c r="K11" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="23.25">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -1294,7 +1303,7 @@
       <c r="J12" s="9"/>
       <c r="K12" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="23.25">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -1307,7 +1316,7 @@
       <c r="J13" s="9"/>
       <c r="K13" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="23.25">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -1320,7 +1329,7 @@
       <c r="J14" s="9"/>
       <c r="K14" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="23.25">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
@@ -1333,7 +1342,7 @@
       <c r="J15" s="9"/>
       <c r="K15" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="23.25">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
@@ -1346,7 +1355,7 @@
       <c r="J16" s="9"/>
       <c r="K16" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="23.25">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -1359,7 +1368,7 @@
       <c r="J17" s="9"/>
       <c r="K17" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="23.25">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -1372,7 +1381,7 @@
       <c r="J18" s="9"/>
       <c r="K18" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="23.25">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -1385,7 +1394,7 @@
       <c r="J19" s="9"/>
       <c r="K19" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="23.25">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -1398,7 +1407,7 @@
       <c r="J20" s="9"/>
       <c r="K20" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="23.25">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -1411,7 +1420,7 @@
       <c r="J21" s="9"/>
       <c r="K21" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="23.25">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -1424,10 +1433,10 @@
       <c r="J22" s="9"/>
       <c r="K22" s="9"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="23.25">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
+      <c r="C23" s="13"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
       <c r="F23" s="9"/>
@@ -1436,32 +1445,6 @@
       <c r="I23" s="9"/>
       <c r="J23" s="9"/>
       <c r="K23" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="17.25">
-      <c r="A24" s="5"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9"/>
-      <c r="K24" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="17.25">
-      <c r="A25" s="5"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
-      <c r="K25" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2004,7 +1987,7 @@
     <col min="12" max="12" style="4" width="51.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="23.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>

--- a/模版/非身份证信息需求.xlsx
+++ b/模版/非身份证信息需求.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="2"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="填写要求"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="51">
   <si>
     <t>姓名</t>
   </si>
@@ -63,6 +63,9 @@
   </si>
   <si>
     <t>余额</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>提取金额</t>
@@ -250,7 +253,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -288,17 +291,26 @@
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -624,230 +636,230 @@
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="23.25">
-      <c r="A1" s="17" t="s">
-        <v>16</v>
+      <c r="A1" s="20" t="s">
+        <v>17</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="23.25">
-      <c r="A2" s="17" t="s">
-        <v>17</v>
+      <c r="A2" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="23.25">
-      <c r="A3" s="17" t="s">
-        <v>18</v>
+      <c r="A3" s="20" t="s">
+        <v>19</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="20.25">
-      <c r="A4" s="18"/>
+      <c r="A4" s="21"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="23.25">
-      <c r="A5" s="17" t="s">
-        <v>19</v>
+      <c r="A5" s="20" t="s">
+        <v>20</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="20.25">
-      <c r="A6" s="18"/>
+      <c r="A6" s="21"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="23.25">
-      <c r="A7" s="19" t="s">
-        <v>20</v>
+      <c r="A7" s="22" t="s">
+        <v>21</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="20.25">
-      <c r="A8" s="18"/>
+      <c r="A8" s="21"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="23.25">
-      <c r="A9" s="19" t="s">
-        <v>21</v>
+      <c r="A9" s="22" t="s">
+        <v>22</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="20.25">
-      <c r="A10" s="18"/>
+      <c r="A10" s="21"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="23.25">
-      <c r="A11" s="19" t="s">
-        <v>22</v>
+      <c r="A11" s="22" t="s">
+        <v>23</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="23.25">
-      <c r="A12" s="17" t="s">
-        <v>23</v>
+      <c r="A12" s="20" t="s">
+        <v>24</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="23.25">
-      <c r="A13" s="17" t="s">
-        <v>24</v>
+      <c r="A13" s="20" t="s">
+        <v>25</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="23.25">
-      <c r="A14" s="17" t="s">
-        <v>25</v>
+      <c r="A14" s="20" t="s">
+        <v>26</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="23.25">
-      <c r="A15" s="19" t="s">
-        <v>26</v>
+      <c r="A15" s="22" t="s">
+        <v>27</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="23.25">
-      <c r="A16" s="20"/>
+      <c r="A16" s="23"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="23.25">
-      <c r="A17" s="19" t="s">
-        <v>27</v>
+      <c r="A17" s="22" t="s">
+        <v>28</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="23.25">
-      <c r="A18" s="20"/>
+      <c r="A18" s="23"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="23.25">
-      <c r="A19" s="19" t="s">
-        <v>28</v>
+      <c r="A19" s="22" t="s">
+        <v>29</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="23.25">
-      <c r="A20" s="19" t="s">
-        <v>29</v>
+      <c r="A20" s="22" t="s">
+        <v>30</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="23.25">
-      <c r="A21" s="19" t="s">
-        <v>30</v>
+      <c r="A21" s="22" t="s">
+        <v>31</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="23.25">
-      <c r="A22" s="20"/>
+      <c r="A22" s="23"/>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="23.25">
-      <c r="A23" s="19" t="s">
-        <v>31</v>
+      <c r="A23" s="22" t="s">
+        <v>32</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="17.25">
-      <c r="A24" s="21"/>
+      <c r="A24" s="24"/>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="23.25">
-      <c r="A25" s="19" t="s">
-        <v>32</v>
+      <c r="A25" s="22" t="s">
+        <v>33</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="17.25">
       <c r="A26" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="23.25">
-      <c r="A27" s="19" t="s">
-        <v>33</v>
+      <c r="A27" s="22" t="s">
+        <v>34</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="17.25">
       <c r="A28" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="23.25">
-      <c r="A29" s="19" t="s">
-        <v>34</v>
+      <c r="A29" s="22" t="s">
+        <v>35</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="17.25">
       <c r="A30" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="17.25">
-      <c r="A31" s="19" t="s">
-        <v>35</v>
+      <c r="A31" s="22" t="s">
+        <v>36</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="17.25">
-      <c r="A32" s="19" t="s">
-        <v>36</v>
+      <c r="A32" s="22" t="s">
+        <v>37</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="17.25">
       <c r="A33" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="17.25">
-      <c r="A34" s="19" t="s">
-        <v>37</v>
+      <c r="A34" s="22" t="s">
+        <v>38</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="17.25">
-      <c r="A35" s="19" t="s">
-        <v>38</v>
+      <c r="A35" s="22" t="s">
+        <v>39</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="17.25">
       <c r="A36" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="17.25">
-      <c r="A37" s="19" t="s">
-        <v>39</v>
+      <c r="A37" s="22" t="s">
+        <v>40</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="17.25">
       <c r="A38" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="17.25">
-      <c r="A39" s="19" t="s">
-        <v>40</v>
+      <c r="A39" s="22" t="s">
+        <v>41</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="17.25">
       <c r="A40" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="17.25">
-      <c r="A41" s="19" t="s">
-        <v>41</v>
+      <c r="A41" s="22" t="s">
+        <v>42</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="17.25">
-      <c r="A42" s="19" t="s">
-        <v>42</v>
+      <c r="A42" s="22" t="s">
+        <v>43</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="17.25">
-      <c r="A43" s="19" t="s">
-        <v>43</v>
+      <c r="A43" s="22" t="s">
+        <v>44</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="17.25">
       <c r="A44" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="17.25">
-      <c r="A45" s="19" t="s">
-        <v>44</v>
+      <c r="A45" s="22" t="s">
+        <v>45</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="17.25">
-      <c r="A46" s="19" t="s">
-        <v>45</v>
+      <c r="A46" s="22" t="s">
+        <v>46</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="17.25">
       <c r="A47" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="17.25">
-      <c r="A48" s="19" t="s">
-        <v>46</v>
+      <c r="A48" s="22" t="s">
+        <v>47</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="17.25">
       <c r="A49" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="17.25">
-      <c r="A50" s="19" t="s">
-        <v>47</v>
+      <c r="A50" s="22" t="s">
+        <v>48</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="17.25">
       <c r="A51" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="17.25">
-      <c r="A52" s="19" t="s">
-        <v>48</v>
+      <c r="A52" s="22" t="s">
+        <v>49</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="17.25">
-      <c r="A53" s="19" t="s">
-        <v>49</v>
+      <c r="A53" s="22" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -867,7 +879,7 @@
     <col min="2" max="2" style="11" width="19.719285714285714" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="11" width="21.862142857142857" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="11" width="48.71928571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="15" width="75.14785714285713" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="19" width="75.14785714285713" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="4" width="9.147857142857141" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="4" width="12.576428571428572" customWidth="1" bestFit="1"/>
     <col min="8" max="8" style="4" width="12.576428571428572" customWidth="1" bestFit="1"/>
@@ -880,7 +892,7 @@
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="17.25">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -891,7 +903,7 @@
       <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="13"/>
+      <c r="E1" s="18"/>
       <c r="F1" s="7"/>
       <c r="G1" s="7"/>
       <c r="H1" s="7"/>
@@ -1110,8 +1122,8 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="11" width="10.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="15" width="23.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="16" width="20.290714285714284" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="11" width="23.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="17" width="20.290714285714284" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="4" width="69.86214285714286" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="4" width="10.862142857142858" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="12" width="10.862142857142858" customWidth="1" bestFit="1"/>
@@ -1126,11 +1138,11 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
-        <v>14</v>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>4</v>
@@ -1407,7 +1419,7 @@
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="23.25">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
-      <c r="C21" s="14"/>
+      <c r="C21" s="16"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
       <c r="F21" s="9"/>
@@ -1459,7 +1471,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -1560,11 +1572,17 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="17.25">
-      <c r="A2" s="5"/>
+      <c r="A2" s="13" t="s">
+        <v>14</v>
+      </c>
       <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
+      <c r="C2" s="14" t="s">
+        <v>14</v>
+      </c>
       <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
+      <c r="E2" s="15" t="s">
+        <v>14</v>
+      </c>
       <c r="F2" s="7"/>
       <c r="G2" s="2"/>
       <c r="H2" s="7"/>
@@ -1576,12 +1594,18 @@
       <c r="N2" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="17.25">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
+      <c r="A3" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="7"/>
+      <c r="E3" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="7"/>
       <c r="G3" s="2"/>
       <c r="H3" s="7"/>
       <c r="I3" s="9"/>
@@ -1594,7 +1618,9 @@
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="17.25">
       <c r="A4" s="5"/>
       <c r="B4" s="5"/>
-      <c r="C4" s="2"/>
+      <c r="C4" s="14" t="s">
+        <v>14</v>
+      </c>
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
@@ -1610,7 +1636,9 @@
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="17.25">
       <c r="A5" s="5"/>
       <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
+      <c r="C5" s="13" t="s">
+        <v>14</v>
+      </c>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
